--- a/results/Int All Data -0.4/Rando_5_permute.xlsx
+++ b/results/Int All Data -0.4/Rando_5_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7938620497604163</v>
+        <v>0.780288844717157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.794169331374413</v>
+        <v>0.7847948415099051</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8075984981611115</v>
+        <v>0.7784871661913404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8082250645771517</v>
+        <v>0.7833244509741788</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8082250645771517</v>
+        <v>0.7842763037862857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8007602819308808</v>
+        <v>0.7820413101719816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8092249301414456</v>
+        <v>0.7817040205878681</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.808279078923362</v>
+        <v>0.7804328829737178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8085863605373587</v>
+        <v>0.7804268813796944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8085863605373587</v>
+        <v>0.7804268813796944</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8088996437453788</v>
+        <v>0.7858787293905261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8067126628832618</v>
+        <v>0.785252162974486</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8073332277052785</v>
+        <v>0.7861920125985462</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8132736054696128</v>
+        <v>0.7858367182323625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8029412611989745</v>
+        <v>0.793343512036797</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8045076772390747</v>
+        <v>0.7911505295806567</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.804543686803215</v>
+        <v>0.7933315088487503</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8054835364272751</v>
+        <v>0.7933315088487503</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8120504806076494</v>
+        <v>0.8074232516156291</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8145987574299733</v>
+        <v>0.8148760310738532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8131523732703406</v>
+        <v>0.8220215289180807</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7941261198974447</v>
+        <v>0.8214129672841106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7928669854713413</v>
+        <v>0.8138281527573723</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7953672495414782</v>
+        <v>0.8138401559454191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7959938159575183</v>
+        <v>0.8138401559454191</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.795065969521505</v>
+        <v>0.8029844726759428</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7953792527295249</v>
+        <v>0.8036050374979595</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7926017150155081</v>
+        <v>0.8125522138680032</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7929330030055983</v>
+        <v>0.8156550379780869</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7879204716772775</v>
+        <v>0.8168961676221205</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7868365837966564</v>
+        <v>0.8223120060688118</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7868725933607966</v>
+        <v>0.8261134157232162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7899994238469737</v>
+        <v>0.832047791893527</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7900054254409972</v>
+        <v>0.8382534401136942</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7972289440075284</v>
+        <v>0.8376028673215606</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.797536225621525</v>
+        <v>0.8433980065105292</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7975062176514083</v>
+        <v>0.8267759917033963</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7971929344433881</v>
+        <v>0.8274445692776001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7943913903532778</v>
+        <v>0.8171614380779535</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7915178271348871</v>
+        <v>0.8140586139678698</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7871978797568634</v>
+        <v>0.813420044363783</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7872338893210037</v>
+        <v>0.8025091464292917</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7869146045189603</v>
+        <v>0.7940565014067736</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7884450109949203</v>
+        <v>0.7940565014067736</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.78719187816284</v>
+        <v>0.7934119302086634</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7953552463534315</v>
+        <v>0.7940384966247035</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7950599679274816</v>
+        <v>0.7925200933367902</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7950599679274816</v>
+        <v>0.8006594551512882</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7950599679274816</v>
+        <v>0.7983452404958757</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7928789886593879</v>
+        <v>0.8037610789425671</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7931742670853379</v>
+        <v>0.7971521236040292</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7881557341629937</v>
+        <v>0.7872542947406831</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7954704769586802</v>
+        <v>0.7872542947406831</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8055195459914153</v>
+        <v>0.7922788292570506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8021034386733117</v>
+        <v>0.7959289987420659</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8021394482374519</v>
+        <v>0.7946758659099857</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7979947474049107</v>
+        <v>0.7839822256791403</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.791717080056463</v>
+        <v>0.7760481183802418</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7898793919665064</v>
+        <v>0.7772652416481818</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.781734028557985</v>
+        <v>0.7864704865612306</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7969768770585468</v>
+        <v>0.7818192511931169</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7969768770585468</v>
+        <v>0.8095694216383872</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7993511076541929</v>
+        <v>0.794681867504009</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8100939609560299</v>
+        <v>0.7893800593437617</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.788670670930199</v>
+        <v>0.7878076417096381</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7655729361718473</v>
+        <v>0.7878076417096381</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.770224171539961</v>
+        <v>0.7884042001555613</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.769910888331941</v>
+        <v>0.7941273202162494</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7749894371945188</v>
+        <v>0.7941273202162494</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7803752676710934</v>
+        <v>0.7908144403153478</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7873455189698384</v>
+        <v>0.7915130258596683</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7852065508599084</v>
+        <v>0.7884042001555613</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7921756018398487</v>
+        <v>0.7968628467721026</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7826150625606161</v>
+        <v>0.7959229971480425</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7813679313225592</v>
+        <v>0.7921287894064664</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7917482883453846</v>
+        <v>0.7868329828402424</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6856869184455392</v>
+        <v>0.7855978547902323</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6863554960197429</v>
+        <v>0.7859111379982524</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6873013472378263</v>
+        <v>0.7853085779583058</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6871813153573589</v>
+        <v>0.7846400003841021</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6741566560078357</v>
+        <v>0.7776949557802553</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6688188382834481</v>
+        <v>0.7776949557802553</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6349506428907518</v>
+        <v>0.751836487771152</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6362457868809956</v>
+        <v>0.7506913836314926</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5867218333189295</v>
+        <v>0.7476485754616427</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6125118831561662</v>
+        <v>0.7331655287644399</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6148248974927741</v>
+        <v>0.7366656583988707</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6110354910264166</v>
+        <v>0.7366116440526604</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5972870394376746</v>
+        <v>0.7474745292349648</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6240229404929949</v>
+        <v>0.7477938140370082</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6527033580118879</v>
+        <v>0.718251567616359</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6336831062330155</v>
+        <v>0.6326880419439402</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4756023199761857</v>
+        <v>0.6435425248946121</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4455763450772525</v>
+        <v>0.622606564303479</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.4384308472330251</v>
+        <v>0.6166601849451214</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.4473516165893662</v>
+        <v>0.6166601849451214</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4253113626979326</v>
+        <v>0.6233291562238931</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4565724656468758</v>
+        <v>0.6233291562238931</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4548139985980276</v>
+        <v>0.7051728939206253</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4530123200722112</v>
+        <v>0.707371877970789</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5032732693803474</v>
+        <v>0.7037457148618673</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6671900056655047</v>
+        <v>0.7031071452577804</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6911663737888782</v>
+        <v>0.6913596251164309</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.68450340410413</v>
+        <v>0.6958704231843977</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.68450340410413</v>
+        <v>0.5949416164933407</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7168099847319449</v>
+        <v>0.5213140610146054</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7006813009535333</v>
+        <v>0.5232057634507725</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7006692977654865</v>
+        <v>0.5166868320225851</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7190077684633038</v>
+        <v>0.5142009717781043</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6605126321551005</v>
+        <v>0.5142009717781043</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6518247246468662</v>
+        <v>0.5217857863048425</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6592534977289968</v>
+        <v>0.4989881312476594</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6592534977289968</v>
+        <v>0.4986688464456159</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6573737984808765</v>
+        <v>0.5012231248619634</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6424094239429993</v>
+        <v>0.5006025600399466</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.635794467010438</v>
+        <v>0.4990121376237529</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6206488443330549</v>
+        <v>0.4964638608014289</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.620058287481155</v>
+        <v>0.4961265712173153</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.616967466559118</v>
+        <v>0.4990181392177763</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6046401924351108</v>
+        <v>0.4993554288018898</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5973818646232439</v>
+        <v>0.4993554288018898</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5826347477890128</v>
+        <v>0.4996747136039332</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5725316644100673</v>
+        <v>0.4996747136039332</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5639829938831753</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5632784067448314</v>
+        <v>0.4999759936239065</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5567294673465273</v>
+        <v>0.4993494272078664</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5811451521524117</v>
+        <v>0.498716859197803</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5606833174891251</v>
+        <v>0.498716859197803</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5547189333486974</v>
+        <v>0.4984035759897829</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5612186596760099</v>
+        <v>0.4984035759897829</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6004762865016948</v>
+        <v>0.4993614303959131</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5093900940089688</v>
+        <v>0.4993614303959131</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5746178184925916</v>
+        <v>0.4990421455938697</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6124434649842998</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6139510654029711</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5684373769673225</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.575944170771757</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.575944170771757</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5809663046505151</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5948635957710369</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5951228646328465</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5951228646328465</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.6176000345691816</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.6164609320235455</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.6164609320235455</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.6186959256378495</v>
+        <v>0.4996807151979566</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.6352999356629121</v>
+        <v>0.4996807151979566</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.6284929277216029</v>
+        <v>0.4996807151979566</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.6198470313715323</v>
+        <v>0.4996807151979566</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5724752494262476</v>
+        <v>0.4996807151979566</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5873087892144153</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.6138130287404334</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.517569066344021</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.517569066344021</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5223643399686957</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
